--- a/input/timetable/Психология служебной деятельности.xlsx
+++ b/input/timetable/Психология служебной деятельности.xlsx
@@ -366,12 +366,6 @@
     <t>Психология отклоняющегося поведения (лек), Г319</t>
   </si>
   <si>
-    <t>Психологическое консультирование (пр), ЭОиДОТ</t>
-  </si>
-  <si>
-    <t>Педагогическая психология (пр), ЭОиДОТ</t>
-  </si>
-  <si>
     <t>Общая психология (пр), Г317</t>
   </si>
   <si>
@@ -400,6 +394,12 @@
   </si>
   <si>
     <t>Анатомия и физиология ЦНС (лек)/(пр), Г306</t>
+  </si>
+  <si>
+    <t>Психологическое консультирование (пр), Г304</t>
+  </si>
+  <si>
+    <t>Педагогическая психология (пр), Г317</t>
   </si>
 </sst>
 </file>
@@ -1351,64 +1351,86 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1422,87 +1444,74 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1515,15 +1524,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1545,68 +1545,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1640,6 +1589,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1650,6 +1611,45 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1670,6 +1670,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1687,15 +1696,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2063,13 +2063,13 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
       <c r="F4" s="4" t="s">
         <v>66</v>
       </c>
@@ -2108,10 +2108,10 @@
       <c r="A7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="115"/>
+      <c r="D7" s="84"/>
       <c r="E7" s="12" t="s">
         <v>68</v>
       </c>
@@ -2162,48 +2162,48 @@
       <c r="B11" s="22">
         <v>1</v>
       </c>
-      <c r="C11" s="119" t="s">
-        <v>123</v>
-      </c>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="121"/>
+      <c r="C11" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="89"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="90"/>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="23"/>
       <c r="B12" s="24">
         <v>2</v>
       </c>
-      <c r="C12" s="122" t="s">
+      <c r="C12" s="91" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="123"/>
-      <c r="E12" s="123"/>
-      <c r="F12" s="124"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="93"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="23"/>
       <c r="B13" s="24">
         <v>3</v>
       </c>
-      <c r="C13" s="109" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="111"/>
+      <c r="C13" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="80"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="23"/>
       <c r="B14" s="24">
         <v>4</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="74"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="71"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="27" t="s">
@@ -2212,46 +2212,46 @@
       <c r="B15" s="28">
         <v>1</v>
       </c>
-      <c r="C15" s="116"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="118"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="87"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="23"/>
       <c r="B16" s="24">
         <v>2</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="74"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="71"/>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="23"/>
       <c r="B17" s="24">
         <v>3</v>
       </c>
-      <c r="C17" s="69" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="71"/>
+      <c r="C17" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="74"/>
     </row>
     <row r="18" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="23"/>
       <c r="B18" s="24">
         <v>4</v>
       </c>
-      <c r="C18" s="106" t="s">
+      <c r="C18" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="108"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="77"/>
     </row>
     <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="27" t="s">
@@ -2260,44 +2260,44 @@
       <c r="B19" s="28">
         <v>1</v>
       </c>
-      <c r="C19" s="112" t="s">
+      <c r="C19" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="113"/>
-      <c r="E19" s="113"/>
-      <c r="F19" s="114"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="83"/>
     </row>
     <row r="20" spans="1:6" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="23"/>
       <c r="B20" s="56">
         <v>2</v>
       </c>
-      <c r="C20" s="109" t="s">
+      <c r="C20" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="111"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="80"/>
     </row>
     <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="23"/>
       <c r="B21" s="24">
         <v>3</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="74"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="71"/>
     </row>
     <row r="22" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="29"/>
       <c r="B22" s="26">
         <v>4</v>
       </c>
-      <c r="C22" s="78"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="80"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="111"/>
     </row>
     <row r="23" spans="1:6" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="27" t="s">
@@ -2306,48 +2306,48 @@
       <c r="B23" s="28">
         <v>1</v>
       </c>
-      <c r="C23" s="75" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="77"/>
+      <c r="C23" s="106" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="107"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="108"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="23"/>
       <c r="B24" s="24">
         <v>2</v>
       </c>
-      <c r="C24" s="72" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="74"/>
+      <c r="C24" s="69" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="71"/>
     </row>
     <row r="25" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="23"/>
       <c r="B25" s="24">
         <v>3</v>
       </c>
-      <c r="C25" s="69" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71"/>
+      <c r="C25" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="74"/>
     </row>
     <row r="26" spans="1:6" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="26">
         <v>4</v>
       </c>
-      <c r="C26" s="81" t="s">
+      <c r="C26" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="83"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="114"/>
     </row>
     <row r="27" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="27" t="s">
@@ -2356,50 +2356,50 @@
       <c r="B27" s="28">
         <v>1</v>
       </c>
-      <c r="C27" s="59" t="s">
+      <c r="C27" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="60"/>
-      <c r="E27" s="63" t="s">
+      <c r="D27" s="116"/>
+      <c r="E27" s="119" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="64"/>
+      <c r="F27" s="120"/>
     </row>
     <row r="28" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="30"/>
       <c r="B28" s="24">
         <v>2</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62" t="s">
+      <c r="D28" s="118"/>
+      <c r="E28" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="F28" s="65"/>
+      <c r="F28" s="121"/>
     </row>
     <row r="29" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="30"/>
       <c r="B29" s="24">
         <v>3</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="68"/>
+      <c r="D29" s="123"/>
+      <c r="E29" s="123"/>
+      <c r="F29" s="124"/>
     </row>
     <row r="30" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="31"/>
       <c r="B30" s="26">
         <v>4</v>
       </c>
-      <c r="C30" s="96"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="97"/>
-      <c r="F30" s="98"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="61"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="32" t="s">
@@ -2408,78 +2408,78 @@
       <c r="B31" s="28">
         <v>1</v>
       </c>
-      <c r="C31" s="87" t="s">
+      <c r="C31" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="89"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="99"/>
     </row>
     <row r="32" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="33"/>
       <c r="B32" s="26">
         <v>2</v>
       </c>
-      <c r="C32" s="103"/>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="105"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="67"/>
+      <c r="F32" s="68"/>
     </row>
     <row r="33" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="34"/>
       <c r="B33" s="35"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
-      <c r="F33" s="92"/>
+      <c r="C33" s="100"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="101"/>
+      <c r="F33" s="102"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="36"/>
       <c r="B34" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="99"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="38"/>
       <c r="B35" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="93" t="s">
+      <c r="C35" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="94"/>
-      <c r="E35" s="94"/>
-      <c r="F35" s="95"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="105"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="51"/>
       <c r="B36" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="100" t="s">
+      <c r="C36" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="101"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="102"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="65"/>
     </row>
     <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="39"/>
       <c r="B37" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="84" t="s">
+      <c r="C37" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="85"/>
-      <c r="E37" s="85"/>
-      <c r="F37" s="86"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="96"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
@@ -2499,6 +2499,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="C36:F36"/>
@@ -2515,21 +2530,6 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2606,13 +2606,13 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
       <c r="F4" s="4" t="s">
         <v>66</v>
       </c>
@@ -2651,10 +2651,10 @@
       <c r="A7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="115"/>
+      <c r="D7" s="84"/>
       <c r="E7" s="12" t="s">
         <v>52</v>
       </c>
@@ -2705,42 +2705,42 @@
       <c r="B11" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="141" t="s">
+      <c r="C11" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="142"/>
-      <c r="E11" s="142"/>
-      <c r="F11" s="143"/>
+      <c r="D11" s="126"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="127"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="23"/>
       <c r="B12" s="22">
         <v>4</v>
       </c>
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="71"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="74"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="23"/>
       <c r="B13" s="24">
         <v>5</v>
       </c>
-      <c r="C13" s="150"/>
-      <c r="D13" s="151"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="152"/>
+      <c r="C13" s="152"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="154"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="25"/>
       <c r="B14" s="26"/>
-      <c r="C14" s="147"/>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="149"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="151"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="27" t="s">
@@ -2749,48 +2749,48 @@
       <c r="B15" s="28">
         <v>1</v>
       </c>
-      <c r="C15" s="126" t="s">
+      <c r="C15" s="156" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="127"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="128"/>
+      <c r="D15" s="157"/>
+      <c r="E15" s="157"/>
+      <c r="F15" s="158"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="23"/>
       <c r="B16" s="24">
         <v>2</v>
       </c>
-      <c r="C16" s="126" t="s">
+      <c r="C16" s="156" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="127"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="128"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="158"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="23"/>
       <c r="B17" s="24">
         <v>3</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="74"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="71"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="29"/>
       <c r="B18" s="26">
         <v>4</v>
       </c>
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="71"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="74"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="27" t="s">
@@ -2799,46 +2799,46 @@
       <c r="B19" s="28">
         <v>1</v>
       </c>
-      <c r="C19" s="156" t="s">
+      <c r="C19" s="131" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="157"/>
-      <c r="E19" s="157"/>
-      <c r="F19" s="158"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="133"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="23"/>
       <c r="B20" s="24">
         <v>2</v>
       </c>
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="71"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="23"/>
       <c r="B21" s="24">
         <v>3</v>
       </c>
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="74"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="29"/>
       <c r="B22" s="26">
         <v>4</v>
       </c>
-      <c r="C22" s="138"/>
-      <c r="D22" s="139"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="140"/>
+      <c r="C22" s="143"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="145"/>
     </row>
     <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="27" t="s">
@@ -2847,48 +2847,48 @@
       <c r="B23" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="141" t="s">
+      <c r="C23" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="D23" s="142"/>
-      <c r="E23" s="142"/>
-      <c r="F23" s="143"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="127"/>
     </row>
     <row r="24" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="23"/>
       <c r="B24" s="22">
         <v>4</v>
       </c>
-      <c r="C24" s="66" t="s">
+      <c r="C24" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="68"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="124"/>
     </row>
     <row r="25" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="23"/>
       <c r="B25" s="24">
         <v>5</v>
       </c>
-      <c r="C25" s="66" t="s">
+      <c r="C25" s="122" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68"/>
+      <c r="D25" s="123"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="124"/>
     </row>
     <row r="26" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="26">
         <v>6</v>
       </c>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="146" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="145"/>
-      <c r="E26" s="145"/>
-      <c r="F26" s="146"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="148"/>
     </row>
     <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="27" t="s">
@@ -2897,44 +2897,44 @@
       <c r="B27" s="28">
         <v>2</v>
       </c>
-      <c r="C27" s="153"/>
-      <c r="D27" s="154"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="155"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="129"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="130"/>
     </row>
     <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="30"/>
       <c r="B28" s="24">
         <v>3</v>
       </c>
-      <c r="C28" s="69" t="s">
+      <c r="C28" s="72" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74"/>
     </row>
     <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="30"/>
       <c r="B29" s="24">
         <v>4</v>
       </c>
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="74"/>
     </row>
     <row r="30" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="31"/>
       <c r="B30" s="26">
         <v>5</v>
       </c>
-      <c r="C30" s="103"/>
-      <c r="D30" s="104"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="105"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="68"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="32" t="s">
@@ -2943,88 +2943,88 @@
       <c r="B31" s="28">
         <v>2</v>
       </c>
-      <c r="C31" s="129" t="s">
+      <c r="C31" s="134" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="130"/>
-      <c r="E31" s="130"/>
-      <c r="F31" s="131"/>
+      <c r="D31" s="135"/>
+      <c r="E31" s="135"/>
+      <c r="F31" s="136"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="38"/>
       <c r="B32" s="24">
         <v>3</v>
       </c>
-      <c r="C32" s="132"/>
-      <c r="D32" s="133"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="134"/>
+      <c r="C32" s="137"/>
+      <c r="D32" s="138"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="139"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="33"/>
       <c r="B33" s="26">
         <v>4</v>
       </c>
-      <c r="C33" s="103"/>
-      <c r="D33" s="104"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="105"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="68"/>
     </row>
     <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="41"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="135"/>
-      <c r="D34" s="136"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="137"/>
+      <c r="C34" s="140"/>
+      <c r="D34" s="141"/>
+      <c r="E34" s="141"/>
+      <c r="F34" s="142"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="36"/>
       <c r="B35" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="87" t="s">
+      <c r="C35" s="97" t="s">
         <v>73</v>
       </c>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="89"/>
+      <c r="D35" s="98"/>
+      <c r="E35" s="98"/>
+      <c r="F35" s="99"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="43"/>
       <c r="B36" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="100" t="s">
+      <c r="C36" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D36" s="101"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="102"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="65"/>
     </row>
     <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="39"/>
       <c r="B37" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="84" t="s">
+      <c r="C37" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="85"/>
-      <c r="E37" s="85"/>
-      <c r="F37" s="86"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="96"/>
     </row>
     <row r="38" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="57" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="58"/>
-      <c r="C38" s="125" t="s">
+      <c r="C38" s="155" t="s">
         <v>80</v>
       </c>
-      <c r="D38" s="125"/>
-      <c r="E38" s="125"/>
-      <c r="F38" s="125"/>
+      <c r="D38" s="155"/>
+      <c r="E38" s="155"/>
+      <c r="F38" s="155"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
@@ -3044,13 +3044,13 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C37:F37"/>
@@ -3067,13 +3067,13 @@
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3155,13 +3155,13 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
       <c r="F4" s="4" t="s">
         <v>66</v>
       </c>
@@ -3200,10 +3200,10 @@
       <c r="A7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="115"/>
+      <c r="D7" s="84"/>
       <c r="E7" s="12" t="s">
         <v>45</v>
       </c>
@@ -3254,44 +3254,44 @@
       <c r="B11" s="22">
         <v>2</v>
       </c>
-      <c r="C11" s="162"/>
-      <c r="D11" s="163"/>
-      <c r="E11" s="163"/>
-      <c r="F11" s="164"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="187"/>
+      <c r="F11" s="188"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="23"/>
       <c r="B12" s="24">
         <v>3</v>
       </c>
-      <c r="C12" s="122"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="123"/>
-      <c r="F12" s="124"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="93"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="23"/>
       <c r="B13" s="24">
         <v>4</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="74"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="25"/>
       <c r="B14" s="26">
         <v>5</v>
       </c>
-      <c r="C14" s="159" t="s">
+      <c r="C14" s="183" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="160"/>
-      <c r="E14" s="160"/>
-      <c r="F14" s="161"/>
+      <c r="D14" s="184"/>
+      <c r="E14" s="184"/>
+      <c r="F14" s="185"/>
     </row>
     <row r="15" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="27" t="s">
@@ -3300,46 +3300,46 @@
       <c r="B15" s="28">
         <v>2</v>
       </c>
-      <c r="C15" s="165" t="s">
+      <c r="C15" s="189" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="166"/>
-      <c r="E15" s="166"/>
-      <c r="F15" s="167"/>
+      <c r="D15" s="190"/>
+      <c r="E15" s="190"/>
+      <c r="F15" s="191"/>
     </row>
     <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="23"/>
       <c r="B16" s="24">
         <v>3</v>
       </c>
-      <c r="C16" s="168" t="s">
+      <c r="C16" s="173" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="169"/>
-      <c r="E16" s="169"/>
-      <c r="F16" s="170"/>
+      <c r="D16" s="174"/>
+      <c r="E16" s="174"/>
+      <c r="F16" s="175"/>
     </row>
     <row r="17" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="23"/>
       <c r="B17" s="24">
         <v>4</v>
       </c>
-      <c r="C17" s="168" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="169"/>
-      <c r="E17" s="194"/>
-      <c r="F17" s="195"/>
+      <c r="C17" s="173" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="174"/>
+      <c r="E17" s="179"/>
+      <c r="F17" s="180"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="29"/>
       <c r="B18" s="26">
         <v>5</v>
       </c>
-      <c r="C18" s="171"/>
-      <c r="D18" s="172"/>
-      <c r="E18" s="172"/>
-      <c r="F18" s="173"/>
+      <c r="C18" s="192"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="194"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="27" t="s">
@@ -3348,44 +3348,44 @@
       <c r="B19" s="28">
         <v>4</v>
       </c>
-      <c r="C19" s="129" t="s">
+      <c r="C19" s="134" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="130"/>
-      <c r="E19" s="130"/>
-      <c r="F19" s="131"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="136"/>
     </row>
     <row r="20" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="23"/>
       <c r="B20" s="24">
         <v>5</v>
       </c>
-      <c r="C20" s="177" t="s">
+      <c r="C20" s="195" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="178"/>
-      <c r="E20" s="178"/>
-      <c r="F20" s="179"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
+      <c r="F20" s="197"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="23"/>
       <c r="B21" s="24">
         <v>6</v>
       </c>
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="74"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="29"/>
       <c r="B22" s="26"/>
-      <c r="C22" s="138"/>
-      <c r="D22" s="139"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="140"/>
+      <c r="C22" s="143"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="145"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="27" t="s">
@@ -3394,46 +3394,46 @@
       <c r="B23" s="28">
         <v>1</v>
       </c>
-      <c r="C23" s="112" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" s="113"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="114"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="83"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="23"/>
       <c r="B24" s="24">
         <v>2</v>
       </c>
-      <c r="C24" s="168" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" s="169"/>
-      <c r="E24" s="169"/>
-      <c r="F24" s="170"/>
+      <c r="C24" s="173" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="174"/>
+      <c r="E24" s="174"/>
+      <c r="F24" s="175"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="23"/>
       <c r="B25" s="24">
         <v>3</v>
       </c>
-      <c r="C25" s="168"/>
-      <c r="D25" s="169"/>
-      <c r="E25" s="169"/>
-      <c r="F25" s="170"/>
+      <c r="C25" s="173" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="174"/>
+      <c r="E25" s="174"/>
+      <c r="F25" s="175"/>
     </row>
     <row r="26" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="26">
         <v>4</v>
       </c>
-      <c r="C26" s="196"/>
-      <c r="D26" s="197"/>
-      <c r="E26" s="82" t="s">
+      <c r="C26" s="181"/>
+      <c r="D26" s="182"/>
+      <c r="E26" s="113" t="s">
         <v>96</v>
       </c>
-      <c r="F26" s="83"/>
+      <c r="F26" s="114"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="27" t="s">
@@ -3442,46 +3442,46 @@
       <c r="B27" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="183" t="s">
+      <c r="C27" s="162" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="184"/>
-      <c r="E27" s="184"/>
-      <c r="F27" s="185"/>
+      <c r="D27" s="163"/>
+      <c r="E27" s="163"/>
+      <c r="F27" s="164"/>
     </row>
     <row r="28" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="30"/>
       <c r="B28" s="24">
         <v>4</v>
       </c>
-      <c r="C28" s="186" t="s">
+      <c r="C28" s="165" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="187"/>
-      <c r="E28" s="187"/>
-      <c r="F28" s="188"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="166"/>
+      <c r="F28" s="167"/>
     </row>
     <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="30"/>
       <c r="B29" s="24">
         <v>5</v>
       </c>
-      <c r="C29" s="186" t="s">
+      <c r="C29" s="165" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="187"/>
-      <c r="E29" s="187"/>
-      <c r="F29" s="188"/>
+      <c r="D29" s="166"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="167"/>
     </row>
     <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="31"/>
       <c r="B30" s="26">
         <v>6</v>
       </c>
-      <c r="C30" s="174"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="176"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="177"/>
+      <c r="E30" s="177"/>
+      <c r="F30" s="178"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="32" t="s">
@@ -3490,64 +3490,64 @@
       <c r="B31" s="28">
         <v>1</v>
       </c>
-      <c r="C31" s="189" t="s">
+      <c r="C31" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="190"/>
-      <c r="E31" s="190"/>
-      <c r="F31" s="64"/>
+      <c r="D31" s="169"/>
+      <c r="E31" s="169"/>
+      <c r="F31" s="120"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="38"/>
       <c r="B32" s="24">
         <v>2</v>
       </c>
-      <c r="C32" s="191"/>
-      <c r="D32" s="192"/>
-      <c r="E32" s="192"/>
-      <c r="F32" s="193"/>
+      <c r="C32" s="170"/>
+      <c r="D32" s="171"/>
+      <c r="E32" s="171"/>
+      <c r="F32" s="172"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="33"/>
       <c r="B33" s="26">
         <v>3</v>
       </c>
-      <c r="C33" s="174"/>
-      <c r="D33" s="175"/>
-      <c r="E33" s="175"/>
-      <c r="F33" s="176"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="177"/>
+      <c r="E33" s="177"/>
+      <c r="F33" s="178"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="34"/>
       <c r="B34" s="55"/>
-      <c r="C34" s="90"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="102"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="53"/>
       <c r="B35" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="180" t="s">
+      <c r="C35" s="159" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="181"/>
-      <c r="E35" s="181"/>
-      <c r="F35" s="182"/>
+      <c r="D35" s="160"/>
+      <c r="E35" s="160"/>
+      <c r="F35" s="161"/>
     </row>
     <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="57" t="s">
         <v>56</v>
       </c>
       <c r="B36" s="58"/>
-      <c r="C36" s="125" t="s">
+      <c r="C36" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="125"/>
-      <c r="E36" s="125"/>
-      <c r="F36" s="125"/>
+      <c r="D36" s="155"/>
+      <c r="E36" s="155"/>
+      <c r="F36" s="155"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
@@ -3567,6 +3567,21 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C27:F27"/>
@@ -3582,21 +3597,6 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3677,13 +3677,13 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
       <c r="F4" s="4" t="s">
         <v>66</v>
       </c>
@@ -3722,10 +3722,10 @@
       <c r="A7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="115"/>
+      <c r="D7" s="84"/>
       <c r="E7" s="12" t="s">
         <v>32</v>
       </c>
@@ -3776,46 +3776,46 @@
       <c r="B11" s="22">
         <v>1</v>
       </c>
-      <c r="C11" s="189" t="s">
+      <c r="C11" s="168" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="190"/>
-      <c r="E11" s="190"/>
-      <c r="F11" s="64"/>
+      <c r="D11" s="169"/>
+      <c r="E11" s="169"/>
+      <c r="F11" s="120"/>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="23"/>
       <c r="B12" s="24">
         <v>2</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="74"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="71"/>
     </row>
     <row r="13" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="23"/>
       <c r="B13" s="24">
         <v>3</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="74"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="25"/>
       <c r="B14" s="26">
         <v>4</v>
       </c>
-      <c r="C14" s="122"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
-      <c r="F14" s="124"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="93"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="27" t="s">
@@ -3824,56 +3824,56 @@
       <c r="B15" s="28">
         <v>2</v>
       </c>
-      <c r="C15" s="156"/>
-      <c r="D15" s="157"/>
-      <c r="E15" s="157"/>
-      <c r="F15" s="158"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="133"/>
     </row>
     <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="23"/>
       <c r="B16" s="24">
         <v>3</v>
       </c>
-      <c r="C16" s="177" t="s">
-        <v>119</v>
-      </c>
-      <c r="D16" s="178"/>
-      <c r="E16" s="178"/>
-      <c r="F16" s="179"/>
+      <c r="C16" s="195" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="196"/>
+      <c r="E16" s="196"/>
+      <c r="F16" s="197"/>
     </row>
     <row r="17" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="23"/>
       <c r="B17" s="24">
         <v>4</v>
       </c>
-      <c r="C17" s="177" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="178"/>
-      <c r="E17" s="178"/>
-      <c r="F17" s="179"/>
+      <c r="C17" s="195" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="196"/>
+      <c r="E17" s="196"/>
+      <c r="F17" s="197"/>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="23"/>
       <c r="B18" s="24">
         <v>5</v>
       </c>
-      <c r="C18" s="72" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="74"/>
+      <c r="C18" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="71"/>
     </row>
     <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="29"/>
       <c r="B19" s="26">
         <v>6</v>
       </c>
-      <c r="C19" s="103"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="105"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="68"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="27" t="s">
@@ -3892,36 +3892,36 @@
       <c r="B21" s="24">
         <v>3</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="74"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="71"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="23"/>
       <c r="B22" s="24">
         <v>4</v>
       </c>
-      <c r="C22" s="100" t="s">
+      <c r="C22" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="101"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="102"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="65"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="23"/>
       <c r="B23" s="24">
         <v>5</v>
       </c>
-      <c r="C23" s="122" t="s">
+      <c r="C23" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="123"/>
-      <c r="E23" s="123"/>
-      <c r="F23" s="124"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="93"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="27" t="s">
@@ -3930,7 +3930,7 @@
       <c r="B24" s="28">
         <v>2</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="115" t="s">
         <v>102</v>
       </c>
       <c r="D24" s="198"/>
@@ -3942,34 +3942,34 @@
       <c r="B25" s="24">
         <v>3</v>
       </c>
-      <c r="C25" s="100" t="s">
+      <c r="C25" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="102"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="65"/>
     </row>
     <row r="26" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="23"/>
       <c r="B26" s="24">
         <v>4</v>
       </c>
-      <c r="C26" s="72" t="s">
+      <c r="C26" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="71"/>
     </row>
     <row r="27" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="29"/>
       <c r="B27" s="26">
         <v>5</v>
       </c>
-      <c r="C27" s="78"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="80"/>
+      <c r="C27" s="109"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="111"/>
     </row>
     <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="27" t="s">
@@ -3978,42 +3978,42 @@
       <c r="B28" s="28">
         <v>2</v>
       </c>
-      <c r="C28" s="156" t="s">
+      <c r="C28" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="157"/>
-      <c r="E28" s="157"/>
-      <c r="F28" s="158"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="133"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="30"/>
       <c r="B29" s="24">
         <v>3</v>
       </c>
-      <c r="C29" s="177"/>
-      <c r="D29" s="178"/>
-      <c r="E29" s="178"/>
-      <c r="F29" s="179"/>
+      <c r="C29" s="195"/>
+      <c r="D29" s="196"/>
+      <c r="E29" s="196"/>
+      <c r="F29" s="197"/>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="30"/>
       <c r="B30" s="24">
         <v>4</v>
       </c>
-      <c r="C30" s="177"/>
-      <c r="D30" s="178"/>
-      <c r="E30" s="178"/>
-      <c r="F30" s="179"/>
+      <c r="C30" s="195"/>
+      <c r="D30" s="196"/>
+      <c r="E30" s="196"/>
+      <c r="F30" s="197"/>
     </row>
     <row r="31" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="31"/>
       <c r="B31" s="26">
         <v>5</v>
       </c>
-      <c r="C31" s="78"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="80"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="111"/>
     </row>
     <row r="32" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="49" t="s">
@@ -4022,7 +4022,7 @@
       <c r="B32" s="22">
         <v>1</v>
       </c>
-      <c r="C32" s="59" t="s">
+      <c r="C32" s="115" t="s">
         <v>97</v>
       </c>
       <c r="D32" s="198"/>
@@ -4034,12 +4034,12 @@
       <c r="B33" s="24">
         <v>2</v>
       </c>
-      <c r="C33" s="72" t="s">
+      <c r="C33" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="74"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="71"/>
     </row>
     <row r="34" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="38"/>
@@ -4056,18 +4056,18 @@
       <c r="B35" s="24">
         <v>4</v>
       </c>
-      <c r="C35" s="132"/>
-      <c r="D35" s="133"/>
-      <c r="E35" s="133"/>
-      <c r="F35" s="134"/>
+      <c r="C35" s="137"/>
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="139"/>
     </row>
     <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="39"/>
       <c r="B36" s="50"/>
-      <c r="C36" s="103"/>
-      <c r="D36" s="104"/>
-      <c r="E36" s="104"/>
-      <c r="F36" s="105"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="68"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
@@ -4087,6 +4087,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
@@ -4103,18 +4115,6 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -4196,13 +4196,13 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
       <c r="F4" s="4" t="s">
         <v>66</v>
       </c>
@@ -4241,10 +4241,10 @@
       <c r="A7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="115"/>
+      <c r="D7" s="84"/>
       <c r="E7" s="12" t="s">
         <v>18</v>
       </c>
@@ -4295,48 +4295,48 @@
       <c r="B11" s="22">
         <v>2</v>
       </c>
-      <c r="C11" s="156" t="s">
+      <c r="C11" s="131" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="158"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="133"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="23"/>
       <c r="B12" s="24">
         <v>3</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="74"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="71"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="23"/>
       <c r="B13" s="24">
         <v>4</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="74"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="25"/>
       <c r="B14" s="26">
         <v>5</v>
       </c>
-      <c r="C14" s="106" t="s">
+      <c r="C14" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="108"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="27" t="s">
@@ -4345,7 +4345,7 @@
       <c r="B15" s="28">
         <v>2</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="115" t="s">
         <v>108</v>
       </c>
       <c r="D15" s="198"/>
@@ -4357,24 +4357,24 @@
       <c r="B16" s="24">
         <v>3</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="74"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="71"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="23"/>
       <c r="B17" s="24">
         <v>4</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="74"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="71"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="29"/>
@@ -4403,34 +4403,34 @@
       <c r="B20" s="24">
         <v>3</v>
       </c>
-      <c r="C20" s="132"/>
-      <c r="D20" s="133"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="134"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="139"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="23"/>
       <c r="B21" s="24">
         <v>4</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="122" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="68"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="124"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="29"/>
       <c r="B22" s="26">
         <v>5</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="74"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="71"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="27" t="s">
@@ -4439,48 +4439,48 @@
       <c r="B23" s="28">
         <v>2</v>
       </c>
-      <c r="C23" s="156" t="s">
+      <c r="C23" s="131" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="157"/>
-      <c r="E23" s="157"/>
-      <c r="F23" s="158"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="133"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="23"/>
       <c r="B24" s="24">
         <v>3</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="74"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="71"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="23"/>
       <c r="B25" s="24">
         <v>4</v>
       </c>
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="71"/>
     </row>
     <row r="26" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="26">
         <v>5</v>
       </c>
-      <c r="C26" s="106" t="s">
+      <c r="C26" s="75" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="108"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="77"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="27" t="s">
@@ -4489,42 +4489,42 @@
       <c r="B27" s="28">
         <v>2</v>
       </c>
-      <c r="C27" s="156" t="s">
+      <c r="C27" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="157"/>
-      <c r="E27" s="157"/>
-      <c r="F27" s="158"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="133"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="30"/>
       <c r="B28" s="24">
         <v>3</v>
       </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="71"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="30"/>
       <c r="B29" s="24">
         <v>4</v>
       </c>
-      <c r="C29" s="209"/>
-      <c r="D29" s="210"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="211"/>
+      <c r="C29" s="212"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="214"/>
     </row>
     <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="31"/>
       <c r="B30" s="26">
         <v>5</v>
       </c>
-      <c r="C30" s="206"/>
-      <c r="D30" s="207"/>
-      <c r="E30" s="207"/>
-      <c r="F30" s="208"/>
+      <c r="C30" s="209"/>
+      <c r="D30" s="210"/>
+      <c r="E30" s="210"/>
+      <c r="F30" s="211"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="49" t="s">
@@ -4533,48 +4533,48 @@
       <c r="B31" s="22">
         <v>1</v>
       </c>
-      <c r="C31" s="156" t="s">
+      <c r="C31" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="157"/>
-      <c r="E31" s="157"/>
-      <c r="F31" s="158"/>
+      <c r="D31" s="132"/>
+      <c r="E31" s="132"/>
+      <c r="F31" s="133"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="38"/>
       <c r="B32" s="24">
         <v>2</v>
       </c>
-      <c r="C32" s="212"/>
-      <c r="D32" s="213"/>
-      <c r="E32" s="213"/>
-      <c r="F32" s="214"/>
+      <c r="C32" s="206"/>
+      <c r="D32" s="207"/>
+      <c r="E32" s="207"/>
+      <c r="F32" s="208"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="38"/>
       <c r="B33" s="24">
         <v>3</v>
       </c>
-      <c r="C33" s="132"/>
-      <c r="D33" s="133"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="134"/>
+      <c r="C33" s="137"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="139"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="38"/>
       <c r="B34" s="24"/>
-      <c r="C34" s="132"/>
-      <c r="D34" s="133"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="134"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="138"/>
+      <c r="E34" s="138"/>
+      <c r="F34" s="139"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="39"/>
       <c r="B35" s="50"/>
-      <c r="C35" s="103"/>
-      <c r="D35" s="104"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="105"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="68"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
@@ -4594,6 +4594,18 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
@@ -4609,18 +4621,6 @@
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>

--- a/input/timetable/Психология служебной деятельности.xlsx
+++ b/input/timetable/Психология служебной деятельности.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14715" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14715" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="26" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="156">
   <si>
     <t>пара</t>
   </si>
@@ -78,6 +78,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>гуманитарного образования и спорта</t>
   </si>
   <si>
@@ -138,6 +141,21 @@
     <t>Русский язык и культура речи (лек 32 ч)</t>
   </si>
   <si>
+    <t>Хадынская А.А.</t>
+  </si>
+  <si>
+    <t>Плеханова Н.П.</t>
+  </si>
+  <si>
+    <t>Усаева Н.Р.</t>
+  </si>
+  <si>
+    <t>Грехова И.П.</t>
+  </si>
+  <si>
+    <t>Шумилов С.П.</t>
+  </si>
+  <si>
     <t>Основы ораторского мастерства (пр), Г305</t>
   </si>
   <si>
@@ -159,15 +177,45 @@
     <t xml:space="preserve">ЭУК </t>
   </si>
   <si>
+    <t>Шибаева Л.В.</t>
+  </si>
+  <si>
+    <t>Гузич М.Э.</t>
+  </si>
+  <si>
     <t>Общая психология (лек), Г306</t>
   </si>
   <si>
+    <t>Родермель Т.А.</t>
+  </si>
+  <si>
+    <t>Бокова Е.В.</t>
+  </si>
+  <si>
+    <t>Шамухаметова Е.С.</t>
+  </si>
+  <si>
+    <t>Леденцова С.Л.</t>
+  </si>
+  <si>
+    <t>Чуранова О.В.</t>
+  </si>
+  <si>
     <t>202-31</t>
   </si>
   <si>
+    <t>Хохлова Н.И.</t>
+  </si>
+  <si>
+    <t>Белоус П.В.</t>
+  </si>
+  <si>
     <t>Психология инклюзивного общества (лекция 16 ч)</t>
   </si>
   <si>
+    <t>Войтович О.Н.</t>
+  </si>
+  <si>
     <t>Базовые теории и методы психотерапии (лек), Г318</t>
   </si>
   <si>
@@ -207,12 +255,21 @@
     <t>Элект. дисциплины по физич. культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины., занятия в объеме 16 часов провдятся по отдельному расписанию.</t>
   </si>
   <si>
+    <t>Осипова А.В.</t>
+  </si>
+  <si>
     <t>Акмеология и геронтопсихология (лек), Г305</t>
   </si>
   <si>
     <t>Акмеология и геронтопсихология (пр), Г305</t>
   </si>
   <si>
+    <t>Вишнягова Е.П.</t>
+  </si>
+  <si>
+    <t>Савостина Л.В.</t>
+  </si>
+  <si>
     <t>Психологическое обеспечение служебной деятельности (лек), Г319//</t>
   </si>
   <si>
@@ -252,6 +309,33 @@
     <t>Психофизиология (лек), Г306</t>
   </si>
   <si>
+    <t>Афян К.А.</t>
+  </si>
+  <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
+    <t>Давыдова А.М.</t>
+  </si>
+  <si>
+    <t>Подлуцкая К.А..; Плеханова Н.П.</t>
+  </si>
+  <si>
+    <t>Плеханова Н.П.; Воробьева А.Д.</t>
+  </si>
+  <si>
+    <t>Мойсеенкова М.А.</t>
+  </si>
+  <si>
+    <t>Меренков В.А.</t>
+  </si>
+  <si>
+    <t>Усаева Н.Р./Меренков В.А.</t>
+  </si>
+  <si>
+    <t>Викулова Е.А.</t>
+  </si>
+  <si>
     <t>Возрастная психология и психология развития (лек), Г306</t>
   </si>
   <si>
@@ -270,6 +354,9 @@
     <t>Элективные дисциплины по физической культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины</t>
   </si>
   <si>
+    <t>Осипова А.В./Шумилов С.П.</t>
+  </si>
+  <si>
     <t>Работа в команде (пр), К428///Психофизиология (пр), Г305</t>
   </si>
   <si>
@@ -279,6 +366,9 @@
     <t>Психология профессионального самоопределения (лек), Г306</t>
   </si>
   <si>
+    <t>Шибаева Л.В./Войтович О.Н.</t>
+  </si>
+  <si>
     <t>//Общая психология (пр), Г306</t>
   </si>
   <si>
@@ -295,6 +385,9 @@
   </si>
   <si>
     <t>//Философия (пр), К427</t>
+  </si>
+  <si>
+    <t>Кочиева Д.И.</t>
   </si>
   <si>
     <t>Специальная психология (лек), Г319// Психология инклюзивного общества (пр), Г319</t>
@@ -511,7 +604,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,6 +623,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -541,7 +640,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -662,6 +761,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -744,6 +901,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1078,6 +1248,17 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -1120,6 +1301,21 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1199,6 +1395,19 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1209,7 +1418,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1243,28 +1452,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1296,10 +1508,11 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1307,395 +1520,425 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2026,7 +2269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2035,10 +2278,11 @@
     <col min="4" max="4" width="16.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2046,15 +2290,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2062,41 +2306,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="127" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
       <c r="F4" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="40"/>
+      <c r="C6" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="42"/>
       <c r="E6" s="7">
         <v>1</v>
       </c>
@@ -2104,46 +2348,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="84"/>
+      <c r="D7" s="143"/>
       <c r="E7" s="12" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>69</v>
+        <v>36</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>88</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
@@ -2154,334 +2398,404 @@
       <c r="D10" s="18"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="23">
         <v>1</v>
       </c>
-      <c r="C11" s="88" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="89"/>
-      <c r="E11" s="89"/>
-      <c r="F11" s="90"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="C11" s="147" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="148"/>
+      <c r="E11" s="148"/>
+      <c r="F11" s="149"/>
+      <c r="G11" s="63" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>2</v>
       </c>
-      <c r="C12" s="91" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="93"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24">
+      <c r="C12" s="150" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="68" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <v>3</v>
       </c>
-      <c r="C13" s="78" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="80"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24">
+      <c r="C13" s="137" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="139"/>
+      <c r="G13" s="73" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25">
         <v>4</v>
       </c>
-      <c r="C14" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="71"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="28">
+      <c r="C14" s="100" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="68" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="29">
         <v>1</v>
       </c>
-      <c r="C15" s="85"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="87"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
+      <c r="C15" s="144"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="145"/>
+      <c r="F15" s="146"/>
+      <c r="G15" s="67"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <v>2</v>
       </c>
-      <c r="C16" s="69" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
+      <c r="C16" s="100" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="101"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="68" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <v>3</v>
       </c>
-      <c r="C17" s="72" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="74"/>
-    </row>
-    <row r="18" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24">
+      <c r="C17" s="97" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="68" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
         <v>4</v>
       </c>
-      <c r="C18" s="75" t="s">
+      <c r="C18" s="134" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="136"/>
+      <c r="G18" s="69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="29">
+        <v>1</v>
+      </c>
+      <c r="C19" s="140" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="141"/>
+      <c r="E19" s="141"/>
+      <c r="F19" s="142"/>
+      <c r="G19" s="78" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="24"/>
+      <c r="B20" s="62">
+        <v>2</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="73" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
+        <v>3</v>
+      </c>
+      <c r="C21" s="100"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="68"/>
+    </row>
+    <row r="22" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="27">
+        <v>4</v>
+      </c>
+      <c r="C22" s="106"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="66"/>
+    </row>
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="29">
+        <v>1</v>
+      </c>
+      <c r="C23" s="103" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="63" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25">
+        <v>2</v>
+      </c>
+      <c r="C24" s="100" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="68" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
+        <v>3</v>
+      </c>
+      <c r="C25" s="97" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="68" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="30"/>
+      <c r="B26" s="27">
+        <v>4</v>
+      </c>
+      <c r="C26" s="109" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="69" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="29">
+        <v>1</v>
+      </c>
+      <c r="C27" s="87" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="88"/>
+      <c r="E27" s="91" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" s="92"/>
+      <c r="G27" s="68" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="25">
+        <v>2</v>
+      </c>
+      <c r="C28" s="89" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="93"/>
+      <c r="G28" s="68" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="31"/>
+      <c r="B29" s="25">
+        <v>3</v>
+      </c>
+      <c r="C29" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="77"/>
-    </row>
-    <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="28">
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="68" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="32"/>
+      <c r="B30" s="27">
+        <v>4</v>
+      </c>
+      <c r="C30" s="124"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="126"/>
+      <c r="G30" s="69"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="29">
         <v>1</v>
       </c>
-      <c r="C19" s="81" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="83"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="56">
+      <c r="C31" s="115" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="116"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="67"/>
+    </row>
+    <row r="32" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="34"/>
+      <c r="B32" s="27">
         <v>2</v>
       </c>
-      <c r="C20" s="78" t="s">
+      <c r="C32" s="131"/>
+      <c r="D32" s="132"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="133"/>
+      <c r="G32" s="66"/>
+    </row>
+    <row r="33" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="35"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="119"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="37"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="38"/>
+      <c r="B34" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="115" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="116"/>
+      <c r="E34" s="116"/>
+      <c r="F34" s="117"/>
+      <c r="G34" s="78" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="40"/>
+      <c r="B35" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="80"/>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
-        <v>3</v>
-      </c>
-      <c r="C21" s="69"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
-    </row>
-    <row r="22" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="26">
-        <v>4</v>
-      </c>
-      <c r="C22" s="109"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="111"/>
-    </row>
-    <row r="23" spans="1:6" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="28">
-        <v>1</v>
-      </c>
-      <c r="C23" s="106" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="108"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24">
-        <v>2</v>
-      </c>
-      <c r="C24" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="71"/>
-    </row>
-    <row r="25" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24">
-        <v>3</v>
-      </c>
-      <c r="C25" s="72" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74"/>
-    </row>
-    <row r="26" spans="1:6" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="26">
-        <v>4</v>
-      </c>
-      <c r="C26" s="112" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="113"/>
-      <c r="E26" s="113"/>
-      <c r="F26" s="114"/>
-    </row>
-    <row r="27" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="28">
-        <v>1</v>
-      </c>
-      <c r="C27" s="115" t="s">
+      <c r="D35" s="122"/>
+      <c r="E35" s="122"/>
+      <c r="F35" s="123"/>
+      <c r="G35" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="116"/>
-      <c r="E27" s="119" t="s">
-        <v>78</v>
-      </c>
-      <c r="F27" s="120"/>
-    </row>
-    <row r="28" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="24">
-        <v>2</v>
-      </c>
-      <c r="C28" s="117" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="121"/>
-    </row>
-    <row r="29" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="24">
-        <v>3</v>
-      </c>
-      <c r="C29" s="122" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="123"/>
-      <c r="E29" s="123"/>
-      <c r="F29" s="124"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="31"/>
-      <c r="B30" s="26">
-        <v>4</v>
-      </c>
-      <c r="C30" s="59"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="61"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="28">
-        <v>1</v>
-      </c>
-      <c r="C31" s="97" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="99"/>
-    </row>
-    <row r="32" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="33"/>
-      <c r="B32" s="26">
-        <v>2</v>
-      </c>
-      <c r="C32" s="66"/>
-      <c r="D32" s="67"/>
-      <c r="E32" s="67"/>
-      <c r="F32" s="68"/>
-    </row>
-    <row r="33" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="34"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="100"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="102"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="36"/>
-      <c r="B34" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="97" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="99"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="38"/>
-      <c r="B35" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="103" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="104"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="105"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="51"/>
-      <c r="B36" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="65"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="39"/>
-      <c r="B37" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="94" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="95"/>
-      <c r="E37" s="95"/>
-      <c r="F37" s="96"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="57"/>
+      <c r="B36" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="128" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="129"/>
+      <c r="E36" s="129"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="76" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="41"/>
+      <c r="B37" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="113"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="114"/>
+      <c r="G37" s="69" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
@@ -2489,7 +2803,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
@@ -2499,21 +2813,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="C36:F36"/>
@@ -2530,6 +2829,21 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C29:F29"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2567,7 +2881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2576,12 +2890,13 @@
     <col min="4" max="4" width="17.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="2"/>
-    <col min="9" max="9" width="9.28515625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.28515625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2589,15 +2904,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2605,41 +2920,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="127" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
       <c r="F4" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="40"/>
+      <c r="C6" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="42"/>
       <c r="E6" s="7">
         <v>2</v>
       </c>
@@ -2647,46 +2962,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="84"/>
+      <c r="D7" s="143"/>
       <c r="E7" s="12" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>69</v>
+        <v>36</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>88</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
@@ -2697,336 +3012,398 @@
       <c r="D10" s="18"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="125" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="126"/>
-      <c r="E11" s="126"/>
-      <c r="F11" s="127"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="22">
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="169" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="170"/>
+      <c r="E11" s="170"/>
+      <c r="F11" s="171"/>
+      <c r="G11" s="67"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="23">
         <v>4</v>
       </c>
-      <c r="C12" s="72" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="74"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24">
+      <c r="C12" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="68" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <v>5</v>
       </c>
-      <c r="C13" s="152"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="153"/>
-      <c r="F13" s="154"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="151"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="28">
+      <c r="C13" s="178"/>
+      <c r="D13" s="179"/>
+      <c r="E13" s="179"/>
+      <c r="F13" s="180"/>
+      <c r="G13" s="68"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="175"/>
+      <c r="D14" s="176"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="177"/>
+      <c r="G14" s="66"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="29">
         <v>1</v>
       </c>
-      <c r="C15" s="156" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="157"/>
-      <c r="E15" s="157"/>
-      <c r="F15" s="158"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
+      <c r="C15" s="154" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="155"/>
+      <c r="E15" s="155"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="79" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <v>2</v>
       </c>
-      <c r="C16" s="156" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="157"/>
-      <c r="E16" s="157"/>
-      <c r="F16" s="158"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
+      <c r="C16" s="154" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="155"/>
+      <c r="E16" s="155"/>
+      <c r="F16" s="156"/>
+      <c r="G16" s="72" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <v>3</v>
       </c>
-      <c r="C17" s="69" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="71"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="26">
+      <c r="C17" s="100" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="101"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="30"/>
+      <c r="B18" s="27">
         <v>4</v>
       </c>
-      <c r="C18" s="72" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="74"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="28">
+      <c r="C18" s="97" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="29">
         <v>1</v>
       </c>
-      <c r="C19" s="131" t="s">
+      <c r="C19" s="184" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="185"/>
+      <c r="E19" s="185"/>
+      <c r="F19" s="186"/>
+      <c r="G19" s="75" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25">
+        <v>2</v>
+      </c>
+      <c r="C20" s="97" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="68" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
+        <v>3</v>
+      </c>
+      <c r="C21" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="72" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="27">
+        <v>4</v>
+      </c>
+      <c r="C22" s="166"/>
+      <c r="D22" s="167"/>
+      <c r="E22" s="167"/>
+      <c r="F22" s="168"/>
+      <c r="G22" s="71"/>
+    </row>
+    <row r="23" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="132"/>
-      <c r="E19" s="132"/>
-      <c r="F19" s="133"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24">
+      <c r="C23" s="169" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="170"/>
+      <c r="E23" s="170"/>
+      <c r="F23" s="171"/>
+      <c r="G23" s="83"/>
+    </row>
+    <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="23">
+        <v>4</v>
+      </c>
+      <c r="C24" s="94" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="84" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
+        <v>5</v>
+      </c>
+      <c r="C25" s="94" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="95"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="72" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="30"/>
+      <c r="B26" s="27">
+        <v>6</v>
+      </c>
+      <c r="C26" s="172" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="173"/>
+      <c r="E26" s="173"/>
+      <c r="F26" s="174"/>
+      <c r="G26" s="71" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="29">
         <v>2</v>
       </c>
-      <c r="C20" s="72" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="74"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
+      <c r="C27" s="181"/>
+      <c r="D27" s="182"/>
+      <c r="E27" s="182"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="63"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="25">
         <v>3</v>
       </c>
-      <c r="C21" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="74"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="26">
+      <c r="C28" s="97" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="98"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="68" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="31"/>
+      <c r="B29" s="25">
         <v>4</v>
       </c>
-      <c r="C22" s="143"/>
-      <c r="D22" s="144"/>
-      <c r="E22" s="144"/>
-      <c r="F22" s="145"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="125" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="127"/>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="22">
+      <c r="C29" s="97" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="68" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="32"/>
+      <c r="B30" s="27">
+        <v>5</v>
+      </c>
+      <c r="C30" s="131"/>
+      <c r="D30" s="132"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="133"/>
+      <c r="G30" s="66"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="29">
+        <v>2</v>
+      </c>
+      <c r="C31" s="157" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="43"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="25">
+        <v>3</v>
+      </c>
+      <c r="C32" s="160"/>
+      <c r="D32" s="161"/>
+      <c r="E32" s="161"/>
+      <c r="F32" s="162"/>
+      <c r="G32" s="44"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="34"/>
+      <c r="B33" s="27">
         <v>4</v>
       </c>
-      <c r="C24" s="122" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="123"/>
-      <c r="E24" s="123"/>
-      <c r="F24" s="124"/>
-    </row>
-    <row r="25" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24">
-        <v>5</v>
-      </c>
-      <c r="C25" s="122" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="123"/>
-      <c r="E25" s="123"/>
-      <c r="F25" s="124"/>
-    </row>
-    <row r="26" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="26">
-        <v>6</v>
-      </c>
-      <c r="C26" s="146" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="147"/>
-      <c r="E26" s="147"/>
-      <c r="F26" s="148"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="28">
-        <v>2</v>
-      </c>
-      <c r="C27" s="128"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="130"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="24">
-        <v>3</v>
-      </c>
-      <c r="C28" s="72" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="24">
-        <v>4</v>
-      </c>
-      <c r="C29" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="31"/>
-      <c r="B30" s="26">
-        <v>5</v>
-      </c>
-      <c r="C30" s="66"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="68"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="28">
-        <v>2</v>
-      </c>
-      <c r="C31" s="134" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="135"/>
-      <c r="E31" s="135"/>
-      <c r="F31" s="136"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="38"/>
-      <c r="B32" s="24">
-        <v>3</v>
-      </c>
-      <c r="C32" s="137"/>
-      <c r="D32" s="138"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="139"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="33"/>
-      <c r="B33" s="26">
-        <v>4</v>
-      </c>
-      <c r="C33" s="66"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
-      <c r="F33" s="68"/>
-    </row>
-    <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="41"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="140"/>
-      <c r="D34" s="141"/>
-      <c r="E34" s="141"/>
-      <c r="F34" s="142"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="36"/>
-      <c r="B35" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="98"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="99"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="43"/>
-      <c r="B36" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="65"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="39"/>
-      <c r="B37" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="94" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="95"/>
-      <c r="E37" s="95"/>
-      <c r="F37" s="96"/>
-    </row>
-    <row r="38" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="58"/>
-      <c r="C38" s="155" t="s">
+      <c r="C33" s="131"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="133"/>
+      <c r="G33" s="45"/>
+    </row>
+    <row r="34" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="46"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="163"/>
+      <c r="D34" s="164"/>
+      <c r="E34" s="164"/>
+      <c r="F34" s="165"/>
+      <c r="G34" s="48"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="38"/>
+      <c r="B35" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="115" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="116"/>
+      <c r="E35" s="116"/>
+      <c r="F35" s="117"/>
+      <c r="G35" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="D38" s="155"/>
-      <c r="E38" s="155"/>
-      <c r="F38" s="155"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="49"/>
+      <c r="B36" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="128" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="129"/>
+      <c r="E36" s="129"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="70" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="41"/>
+      <c r="B37" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="112" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="113"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="114"/>
+      <c r="G37" s="69" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="65"/>
+      <c r="C38" s="153" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" s="153"/>
+      <c r="E38" s="153"/>
+      <c r="F38" s="153"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
@@ -3034,7 +3411,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
@@ -3044,13 +3421,13 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C37:F37"/>
@@ -3067,13 +3444,13 @@
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3118,7 +3495,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3127,10 +3504,11 @@
     <col min="4" max="4" width="18.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3138,15 +3516,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3154,41 +3532,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="127" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
       <c r="F4" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="40"/>
+      <c r="C6" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="42"/>
       <c r="E6" s="7">
         <v>3</v>
       </c>
@@ -3196,360 +3574,416 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="84"/>
+      <c r="D7" s="143"/>
       <c r="E7" s="12" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>70</v>
+        <v>36</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>89</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="48"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="D10" s="52"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="23">
         <v>2</v>
       </c>
-      <c r="C11" s="186"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="187"/>
-      <c r="F11" s="188"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="C11" s="190"/>
+      <c r="D11" s="191"/>
+      <c r="E11" s="191"/>
+      <c r="F11" s="192"/>
+      <c r="G11" s="72"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="93"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24">
+      <c r="C12" s="150"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="72"/>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <v>4</v>
       </c>
-      <c r="C13" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="71"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="C13" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <v>5</v>
       </c>
-      <c r="C14" s="183" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="184"/>
-      <c r="E14" s="184"/>
-      <c r="F14" s="185"/>
-    </row>
-    <row r="15" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="28">
+      <c r="C14" s="187" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="188"/>
+      <c r="E14" s="188"/>
+      <c r="F14" s="189"/>
+      <c r="G14" s="72" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="29">
         <v>2</v>
       </c>
-      <c r="C15" s="189" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="190"/>
-      <c r="E15" s="190"/>
-      <c r="F15" s="191"/>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
+      <c r="C15" s="193" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="194"/>
+      <c r="E15" s="194"/>
+      <c r="F15" s="195"/>
+      <c r="G15" s="78" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <v>3</v>
       </c>
-      <c r="C16" s="173" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="174"/>
-      <c r="E16" s="174"/>
-      <c r="F16" s="175"/>
-    </row>
-    <row r="17" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
+      <c r="C16" s="196" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="197"/>
+      <c r="E16" s="197"/>
+      <c r="F16" s="198"/>
+      <c r="G16" s="68" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <v>4</v>
       </c>
-      <c r="C17" s="173" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="174"/>
-      <c r="E17" s="179"/>
-      <c r="F17" s="180"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="26">
+      <c r="C17" s="196" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="197"/>
+      <c r="E17" s="222"/>
+      <c r="F17" s="223"/>
+      <c r="G17" s="68" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="30"/>
+      <c r="B18" s="27">
         <v>5</v>
       </c>
-      <c r="C18" s="192"/>
-      <c r="D18" s="193"/>
-      <c r="E18" s="193"/>
-      <c r="F18" s="194"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="28">
+      <c r="C18" s="199"/>
+      <c r="D18" s="200"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="201"/>
+      <c r="G18" s="74"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="29">
         <v>4</v>
       </c>
-      <c r="C19" s="134" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="135"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="136"/>
-    </row>
-    <row r="20" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24">
+      <c r="C19" s="157" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="158"/>
+      <c r="E19" s="158"/>
+      <c r="F19" s="159"/>
+      <c r="G19" s="79" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25">
         <v>5</v>
       </c>
-      <c r="C20" s="195" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="196"/>
-      <c r="E20" s="196"/>
-      <c r="F20" s="197"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
+      <c r="C20" s="205" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="206"/>
+      <c r="E20" s="206"/>
+      <c r="F20" s="207"/>
+      <c r="G20" s="72" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
         <v>6</v>
       </c>
-      <c r="C21" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="74"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="143"/>
-      <c r="D22" s="144"/>
-      <c r="E22" s="144"/>
-      <c r="F22" s="145"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="28">
+      <c r="C21" s="97" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="72" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="166"/>
+      <c r="D22" s="167"/>
+      <c r="E22" s="167"/>
+      <c r="F22" s="168"/>
+      <c r="G22" s="71"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="29">
         <v>1</v>
       </c>
-      <c r="C23" s="81"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="82"/>
-      <c r="F23" s="83"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24">
+      <c r="C23" s="140"/>
+      <c r="D23" s="141"/>
+      <c r="E23" s="141"/>
+      <c r="F23" s="142"/>
+      <c r="G23" s="78"/>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25">
         <v>2</v>
       </c>
-      <c r="C24" s="173" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" s="174"/>
-      <c r="E24" s="174"/>
-      <c r="F24" s="175"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24">
+      <c r="C24" s="196" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="197"/>
+      <c r="E24" s="197"/>
+      <c r="F24" s="198"/>
+      <c r="G24" s="86" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
         <v>3</v>
       </c>
-      <c r="C25" s="173" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" s="174"/>
-      <c r="E25" s="174"/>
-      <c r="F25" s="175"/>
-    </row>
-    <row r="26" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="26">
+      <c r="C25" s="196" t="s">
+        <v>154</v>
+      </c>
+      <c r="D25" s="197"/>
+      <c r="E25" s="197"/>
+      <c r="F25" s="198"/>
+      <c r="G25" s="86" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="30"/>
+      <c r="B26" s="27">
         <v>4</v>
       </c>
-      <c r="C26" s="181"/>
-      <c r="D26" s="182"/>
-      <c r="E26" s="113" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="114"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="162" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="163"/>
-      <c r="E27" s="163"/>
-      <c r="F27" s="164"/>
-    </row>
-    <row r="28" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="24">
+      <c r="C26" s="224"/>
+      <c r="D26" s="225"/>
+      <c r="E26" s="110" t="s">
+        <v>127</v>
+      </c>
+      <c r="F26" s="111"/>
+      <c r="G26" s="68" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="211" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="212"/>
+      <c r="E27" s="212"/>
+      <c r="F27" s="213"/>
+      <c r="G27" s="43"/>
+    </row>
+    <row r="28" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="25">
         <v>4</v>
       </c>
-      <c r="C28" s="165" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="166"/>
-      <c r="E28" s="166"/>
-      <c r="F28" s="167"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="24">
+      <c r="C28" s="214" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="215"/>
+      <c r="E28" s="215"/>
+      <c r="F28" s="216"/>
+      <c r="G28" s="80" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="31"/>
+      <c r="B29" s="25">
         <v>5</v>
       </c>
-      <c r="C29" s="165" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="166"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="167"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="31"/>
-      <c r="B30" s="26">
+      <c r="C29" s="214" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" s="215"/>
+      <c r="E29" s="215"/>
+      <c r="F29" s="216"/>
+      <c r="G29" s="80" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="32"/>
+      <c r="B30" s="27">
         <v>6</v>
       </c>
-      <c r="C30" s="176"/>
-      <c r="D30" s="177"/>
-      <c r="E30" s="177"/>
-      <c r="F30" s="178"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="28">
+      <c r="C30" s="202"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="204"/>
+      <c r="G30" s="45"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="29">
         <v>1</v>
       </c>
-      <c r="C31" s="168" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="169"/>
-      <c r="E31" s="169"/>
-      <c r="F31" s="120"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="38"/>
-      <c r="B32" s="24">
+      <c r="C31" s="217" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="218"/>
+      <c r="E31" s="218"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="43"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="25">
         <v>2</v>
       </c>
-      <c r="C32" s="170"/>
-      <c r="D32" s="171"/>
-      <c r="E32" s="171"/>
-      <c r="F32" s="172"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="33"/>
-      <c r="B33" s="26">
+      <c r="C32" s="219"/>
+      <c r="D32" s="220"/>
+      <c r="E32" s="220"/>
+      <c r="F32" s="221"/>
+      <c r="G32" s="44"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="34"/>
+      <c r="B33" s="27">
         <v>3</v>
       </c>
-      <c r="C33" s="176"/>
-      <c r="D33" s="177"/>
-      <c r="E33" s="177"/>
-      <c r="F33" s="178"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="34"/>
-      <c r="B34" s="55"/>
-      <c r="C34" s="100"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="102"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="53"/>
-      <c r="B35" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="159" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="160"/>
-      <c r="E35" s="160"/>
-      <c r="F35" s="161"/>
-    </row>
-    <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="58"/>
-      <c r="C36" s="155" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="155"/>
-      <c r="E36" s="155"/>
-      <c r="F36" s="155"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="202"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="204"/>
+      <c r="G33" s="45"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="35"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="118"/>
+      <c r="D34" s="119"/>
+      <c r="E34" s="119"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="37"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="59"/>
+      <c r="B35" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="208" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="209"/>
+      <c r="E35" s="209"/>
+      <c r="F35" s="210"/>
+      <c r="G35" s="77" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="65"/>
+      <c r="C36" s="153" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="153"/>
+      <c r="E36" s="153"/>
+      <c r="F36" s="153"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
         <v>15</v>
       </c>
@@ -3557,7 +3991,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
@@ -3567,6 +4001,21 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C7:D7"/>
@@ -3582,21 +4031,6 @@
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3641,7 +4075,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3649,10 +4083,11 @@
     <col min="3" max="3" width="20" style="2" customWidth="1"/>
     <col min="4" max="5" width="19" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.28515625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3660,15 +4095,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3676,41 +4111,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="127" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
       <c r="F4" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="40"/>
+      <c r="C6" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="42"/>
       <c r="E6" s="7">
         <v>4</v>
       </c>
@@ -3718,358 +4153,415 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="84"/>
+      <c r="D7" s="143"/>
       <c r="E7" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>71</v>
+        <v>36</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>90</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="48"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="D10" s="52"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="23">
         <v>1</v>
       </c>
-      <c r="C11" s="168" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="169"/>
-      <c r="E11" s="169"/>
-      <c r="F11" s="120"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="C11" s="217" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="218"/>
+      <c r="E11" s="218"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="79" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>2</v>
       </c>
-      <c r="C12" s="69" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="71"/>
-    </row>
-    <row r="13" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24">
+      <c r="C12" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="72" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <v>3</v>
       </c>
-      <c r="C13" s="69" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="71"/>
-    </row>
-    <row r="14" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="C13" s="100" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="72" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <v>4</v>
       </c>
-      <c r="C14" s="91"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="92"/>
-      <c r="F14" s="93"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="28">
+      <c r="C14" s="150"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="71"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="29">
         <v>2</v>
       </c>
-      <c r="C15" s="131"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="133"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
+      <c r="C15" s="184"/>
+      <c r="D15" s="185"/>
+      <c r="E15" s="185"/>
+      <c r="F15" s="186"/>
+      <c r="G15" s="81"/>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <v>3</v>
       </c>
-      <c r="C16" s="195" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="196"/>
-      <c r="E16" s="196"/>
-      <c r="F16" s="197"/>
-    </row>
-    <row r="17" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
+      <c r="C16" s="205" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
+      <c r="F16" s="207"/>
+      <c r="G16" s="82" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <v>4</v>
       </c>
-      <c r="C17" s="195" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="196"/>
-      <c r="E17" s="196"/>
-      <c r="F17" s="197"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24">
+      <c r="C17" s="205" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="206"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="207"/>
+      <c r="G17" s="72" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
         <v>5</v>
       </c>
-      <c r="C18" s="69" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="71"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="29"/>
-      <c r="B19" s="26">
+      <c r="C18" s="100" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="101"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="72" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="30"/>
+      <c r="B19" s="27">
         <v>6</v>
       </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="68"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="28">
+      <c r="C19" s="131"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="45"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="29">
         <v>2</v>
       </c>
-      <c r="C20" s="203"/>
-      <c r="D20" s="204"/>
-      <c r="E20" s="204"/>
-      <c r="F20" s="205"/>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
+      <c r="C20" s="231"/>
+      <c r="D20" s="232"/>
+      <c r="E20" s="232"/>
+      <c r="F20" s="233"/>
+      <c r="G20" s="43"/>
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
         <v>3</v>
       </c>
-      <c r="C21" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24">
+      <c r="C21" s="100" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="101"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="72" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25">
         <v>4</v>
       </c>
-      <c r="C22" s="63" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="65"/>
-    </row>
-    <row r="23" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24">
+      <c r="C22" s="128" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="129"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="72" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="24"/>
+      <c r="B23" s="25">
         <v>5</v>
       </c>
-      <c r="C23" s="91" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="93"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="28">
+      <c r="C23" s="150" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="151"/>
+      <c r="E23" s="151"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="71" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="29">
         <v>2</v>
       </c>
-      <c r="C24" s="115" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="198"/>
-      <c r="E24" s="198"/>
-      <c r="F24" s="199"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24">
+      <c r="C24" s="87" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="226"/>
+      <c r="E24" s="226"/>
+      <c r="F24" s="227"/>
+      <c r="G24" s="79" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
         <v>3</v>
       </c>
-      <c r="C25" s="63" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="65"/>
-    </row>
-    <row r="26" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24">
+      <c r="C25" s="128" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" s="129"/>
+      <c r="E25" s="129"/>
+      <c r="F25" s="130"/>
+      <c r="G25" s="72" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25">
         <v>4</v>
       </c>
-      <c r="C26" s="69" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="71"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="29"/>
-      <c r="B27" s="26">
+      <c r="C26" s="100" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="101"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="30"/>
+      <c r="B27" s="27">
         <v>5</v>
       </c>
-      <c r="C27" s="109"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="111"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="28">
+      <c r="C27" s="106"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="71"/>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="29">
         <v>2</v>
       </c>
-      <c r="C28" s="131" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="132"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="133"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="24">
+      <c r="C28" s="184" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="185"/>
+      <c r="E28" s="185"/>
+      <c r="F28" s="186"/>
+      <c r="G28" s="81"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="31"/>
+      <c r="B29" s="25">
         <v>3</v>
       </c>
-      <c r="C29" s="195"/>
-      <c r="D29" s="196"/>
-      <c r="E29" s="196"/>
-      <c r="F29" s="197"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="30"/>
-      <c r="B30" s="24">
+      <c r="C29" s="205"/>
+      <c r="D29" s="206"/>
+      <c r="E29" s="206"/>
+      <c r="F29" s="207"/>
+      <c r="G29" s="82"/>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="31"/>
+      <c r="B30" s="25">
         <v>4</v>
       </c>
-      <c r="C30" s="195"/>
-      <c r="D30" s="196"/>
-      <c r="E30" s="196"/>
-      <c r="F30" s="197"/>
-    </row>
-    <row r="31" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="31"/>
-      <c r="B31" s="26">
+      <c r="C30" s="205"/>
+      <c r="D30" s="206"/>
+      <c r="E30" s="206"/>
+      <c r="F30" s="207"/>
+      <c r="G30" s="72"/>
+    </row>
+    <row r="31" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="32"/>
+      <c r="B31" s="27">
         <v>5</v>
       </c>
-      <c r="C31" s="109"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="111"/>
-    </row>
-    <row r="32" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="22">
+      <c r="C31" s="106"/>
+      <c r="D31" s="107"/>
+      <c r="E31" s="107"/>
+      <c r="F31" s="108"/>
+      <c r="G31" s="45"/>
+    </row>
+    <row r="32" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="23">
         <v>1</v>
       </c>
-      <c r="C32" s="115" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" s="198"/>
-      <c r="E32" s="198"/>
-      <c r="F32" s="199"/>
-    </row>
-    <row r="33" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="38"/>
-      <c r="B33" s="24">
+      <c r="C32" s="87" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="226"/>
+      <c r="E32" s="226"/>
+      <c r="F32" s="227"/>
+      <c r="G32" s="81" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="40"/>
+      <c r="B33" s="25">
         <v>2</v>
       </c>
-      <c r="C33" s="69" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="71"/>
-    </row>
-    <row r="34" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="38"/>
-      <c r="B34" s="24">
+      <c r="C33" s="100" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" s="101"/>
+      <c r="E33" s="101"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="72" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="40"/>
+      <c r="B34" s="25">
         <v>3</v>
       </c>
-      <c r="C34" s="200"/>
-      <c r="D34" s="201"/>
-      <c r="E34" s="201"/>
-      <c r="F34" s="202"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="38"/>
-      <c r="B35" s="24">
+      <c r="C34" s="228"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="230"/>
+      <c r="G34" s="72"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="40"/>
+      <c r="B35" s="25">
         <v>4</v>
       </c>
-      <c r="C35" s="137"/>
-      <c r="D35" s="138"/>
-      <c r="E35" s="138"/>
-      <c r="F35" s="139"/>
-    </row>
-    <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="39"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="66"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="68"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C35" s="160"/>
+      <c r="D35" s="161"/>
+      <c r="E35" s="161"/>
+      <c r="F35" s="162"/>
+      <c r="G35" s="44"/>
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="41"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="131"/>
+      <c r="D36" s="132"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="133"/>
+      <c r="G36" s="45"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
         <v>15</v>
       </c>
@@ -4077,7 +4569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -4087,18 +4579,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
@@ -4115,6 +4595,18 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -4159,7 +4651,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -4168,10 +4660,11 @@
     <col min="4" max="4" width="17" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -4179,15 +4672,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -4195,41 +4688,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="127" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
       <c r="F4" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="40"/>
+      <c r="C6" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="42"/>
       <c r="E6" s="7">
         <v>5</v>
       </c>
@@ -4237,346 +4730,400 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="84"/>
+      <c r="D7" s="143"/>
       <c r="E7" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>91</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="48"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="D10" s="52"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="23">
         <v>2</v>
       </c>
-      <c r="C11" s="131" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="133"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="C11" s="184" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="186"/>
+      <c r="G11" s="79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="69" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="71"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24">
+      <c r="C12" s="100" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <v>4</v>
       </c>
-      <c r="C13" s="69" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="71"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="C13" s="100" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="72" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <v>5</v>
       </c>
-      <c r="C14" s="75" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="77"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="28">
+      <c r="C14" s="134" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="135"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="72" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="29">
         <v>2</v>
       </c>
-      <c r="C15" s="115" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="198"/>
-      <c r="E15" s="198"/>
-      <c r="F15" s="199"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
+      <c r="C15" s="87" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="226"/>
+      <c r="E15" s="226"/>
+      <c r="F15" s="227"/>
+      <c r="G15" s="79" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <v>3</v>
       </c>
-      <c r="C16" s="69" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
+      <c r="C16" s="100" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="101"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="72" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <v>4</v>
       </c>
-      <c r="C17" s="69" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="71"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="26">
+      <c r="C17" s="100" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="101"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="72" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="30"/>
+      <c r="B18" s="27">
         <v>5</v>
       </c>
-      <c r="C18" s="200"/>
-      <c r="D18" s="201"/>
-      <c r="E18" s="201"/>
-      <c r="F18" s="202"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="28">
+      <c r="C18" s="228"/>
+      <c r="D18" s="229"/>
+      <c r="E18" s="229"/>
+      <c r="F18" s="230"/>
+      <c r="G18" s="85"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="29">
         <v>2</v>
       </c>
-      <c r="C19" s="203"/>
-      <c r="D19" s="204"/>
-      <c r="E19" s="204"/>
-      <c r="F19" s="205"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24">
+      <c r="C19" s="231"/>
+      <c r="D19" s="232"/>
+      <c r="E19" s="232"/>
+      <c r="F19" s="233"/>
+      <c r="G19" s="79"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25">
         <v>3</v>
       </c>
-      <c r="C20" s="137"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="138"/>
-      <c r="F20" s="139"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
+      <c r="C20" s="160"/>
+      <c r="D20" s="161"/>
+      <c r="E20" s="161"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="72"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
         <v>4</v>
       </c>
-      <c r="C21" s="122" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
-      <c r="F21" s="124"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="26">
+      <c r="C21" s="94" t="s">
+        <v>143</v>
+      </c>
+      <c r="D21" s="95"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="72" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="27">
         <v>5</v>
       </c>
-      <c r="C22" s="69" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="71"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="28">
+      <c r="C22" s="100" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="101"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="102"/>
+      <c r="G22" s="71" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="29">
         <v>2</v>
       </c>
-      <c r="C23" s="131" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" s="132"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="133"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24">
+      <c r="C23" s="184" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="185"/>
+      <c r="E23" s="185"/>
+      <c r="F23" s="186"/>
+      <c r="G23" s="79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25">
         <v>3</v>
       </c>
-      <c r="C24" s="69" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="71"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24">
+      <c r="C24" s="100" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
         <v>4</v>
       </c>
-      <c r="C25" s="69" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="26">
+      <c r="C25" s="100" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="72" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="30"/>
+      <c r="B26" s="27">
         <v>5</v>
       </c>
-      <c r="C26" s="75" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="77"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="28">
+      <c r="C26" s="134" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="135"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="136"/>
+      <c r="G26" s="71" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="29">
         <v>2</v>
       </c>
-      <c r="C27" s="131" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="132"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="133"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="24">
+      <c r="C27" s="184" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="185"/>
+      <c r="E27" s="185"/>
+      <c r="F27" s="186"/>
+      <c r="G27" s="79"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="25">
         <v>3</v>
       </c>
-      <c r="C28" s="69"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="24">
+      <c r="C28" s="100"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="72"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="31"/>
+      <c r="B29" s="25">
         <v>4</v>
       </c>
-      <c r="C29" s="212"/>
-      <c r="D29" s="213"/>
-      <c r="E29" s="213"/>
-      <c r="F29" s="214"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="31"/>
-      <c r="B30" s="26">
+      <c r="C29" s="237"/>
+      <c r="D29" s="238"/>
+      <c r="E29" s="238"/>
+      <c r="F29" s="239"/>
+      <c r="G29" s="72"/>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="32"/>
+      <c r="B30" s="27">
         <v>5</v>
       </c>
-      <c r="C30" s="209"/>
-      <c r="D30" s="210"/>
-      <c r="E30" s="210"/>
-      <c r="F30" s="211"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="22">
+      <c r="C30" s="234"/>
+      <c r="D30" s="235"/>
+      <c r="E30" s="235"/>
+      <c r="F30" s="236"/>
+      <c r="G30" s="45"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="23">
         <v>1</v>
       </c>
-      <c r="C31" s="131" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="132"/>
-      <c r="E31" s="132"/>
-      <c r="F31" s="133"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="38"/>
-      <c r="B32" s="24">
+      <c r="C31" s="184" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="185"/>
+      <c r="E31" s="185"/>
+      <c r="F31" s="186"/>
+      <c r="G31" s="79"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="25">
         <v>2</v>
       </c>
-      <c r="C32" s="206"/>
-      <c r="D32" s="207"/>
-      <c r="E32" s="207"/>
-      <c r="F32" s="208"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="38"/>
-      <c r="B33" s="24">
+      <c r="C32" s="240"/>
+      <c r="D32" s="241"/>
+      <c r="E32" s="241"/>
+      <c r="F32" s="242"/>
+      <c r="G32" s="72"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="40"/>
+      <c r="B33" s="25">
         <v>3</v>
       </c>
-      <c r="C33" s="137"/>
-      <c r="D33" s="138"/>
-      <c r="E33" s="138"/>
-      <c r="F33" s="139"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="38"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="137"/>
-      <c r="D34" s="138"/>
-      <c r="E34" s="138"/>
-      <c r="F34" s="139"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="39"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="68"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="160"/>
+      <c r="D33" s="161"/>
+      <c r="E33" s="161"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="44"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="40"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="161"/>
+      <c r="E34" s="161"/>
+      <c r="F34" s="162"/>
+      <c r="G34" s="44"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="41"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="131"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="132"/>
+      <c r="F35" s="133"/>
+      <c r="G35" s="45"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
         <v>15</v>
       </c>
@@ -4584,7 +5131,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
@@ -4594,18 +5141,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
@@ -4621,6 +5156,18 @@
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
